--- a/3_meta-analysis/data/reformatted/xlsx/ikdc_subjective.xlsx
+++ b/3_meta-analysis/data/reformatted/xlsx/ikdc_subjective.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T35"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +424,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>study1</t>
+          <t>study</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>study2</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -454,12 +454,12 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>y1</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>y2</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -474,42 +474,62 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>age1</t>
+          <t>age_mean1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>age2</t>
+          <t>age_mean2</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>age_sd1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>age_sd2</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>male1</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>male2</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>female1</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>female2</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>follow_up1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>follow_up2</t>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>follow-up_mo1</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>follow-up_mo2</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>follow-up_yr1</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>follow-up_yr2</t>
         </is>
       </c>
     </row>
@@ -518,16 +538,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aglietti et al., 2004</t>
+          <t>Barié et al., 2020</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aglietti et al., 2004</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -537,50 +557,62 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HT</t>
+          <t>QT</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>91</v>
       </c>
       <c r="J2" t="n">
-        <v>1.95</v>
+        <v>92</v>
       </c>
       <c r="K2" t="n">
-        <v>1.08</v>
+        <v>7.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>11.5</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>30.6</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>30.6</v>
       </c>
       <c r="O2" t="n">
-        <v>46</v>
+        <v>7.5</v>
       </c>
       <c r="P2" t="n">
-        <v>46</v>
+        <v>7.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S2" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="U2" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="3">
@@ -588,69 +620,81 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ahldén et al., 2009</t>
+          <t>Bi et al., 2018</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ahldén et al., 2009</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BPTB</t>
+          <t>HT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HT</t>
+          <t>PLT</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="H3" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4</v>
+        <v>89.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>7.1</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>8.4</v>
       </c>
       <c r="M3" t="n">
-        <v>28.6</v>
+        <v>27.9</v>
       </c>
       <c r="N3" t="n">
-        <v>28.6</v>
+        <v>27.9</v>
       </c>
       <c r="O3" t="n">
-        <v>18</v>
+        <v>6.7</v>
       </c>
       <c r="P3" t="n">
-        <v>18</v>
+        <v>6.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="S3" t="n">
-        <v>86.8</v>
+        <v>31</v>
       </c>
       <c r="T3" t="n">
-        <v>86.8</v>
+        <v>31</v>
+      </c>
+      <c r="U3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -658,16 +702,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Anderson et al., 2001</t>
+          <t>Björnsson et al., 2016</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Anderson et al., 2001</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -681,46 +725,58 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="H4" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1</v>
+        <v>67.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>74</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>20.8</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>18.8</v>
       </c>
       <c r="M4" t="n">
-        <v>21</v>
+        <v>28.2</v>
       </c>
       <c r="N4" t="n">
-        <v>21</v>
+        <v>28.2</v>
       </c>
       <c r="O4" t="n">
-        <v>45</v>
+        <v>9.1</v>
       </c>
       <c r="P4" t="n">
-        <v>45</v>
+        <v>9.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="R4" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="S4" t="n">
-        <v>35.8</v>
+        <v>19</v>
       </c>
       <c r="T4" t="n">
-        <v>35.8</v>
+        <v>19</v>
+      </c>
+      <c r="U4" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="V4" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X4" t="n">
+        <v>16.9</v>
       </c>
     </row>
     <row r="5">
@@ -728,69 +784,81 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bottoni et al., 2015</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ikdc_subjective</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>44</v>
+      </c>
+      <c r="H5" t="n">
+        <v>36</v>
+      </c>
+      <c r="I5" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>41</v>
+      </c>
+      <c r="R5" t="n">
+        <v>41</v>
+      </c>
+      <c r="S5" t="n">
         <v>7</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Aune et al., 2001</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Aune et al., 2001</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>BPTB</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>32</v>
-      </c>
-      <c r="H5" t="n">
-        <v>29</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>27</v>
-      </c>
-      <c r="N5" t="n">
-        <v>27</v>
-      </c>
-      <c r="O5" t="n">
-        <v>21</v>
-      </c>
-      <c r="P5" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>16</v>
-      </c>
-      <c r="R5" t="n">
-        <v>16</v>
-      </c>
-      <c r="S5" t="n">
-        <v>24</v>
-      </c>
       <c r="T5" t="n">
-        <v>24</v>
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>120</v>
+      </c>
+      <c r="V5" t="n">
+        <v>120</v>
+      </c>
+      <c r="W5" t="n">
+        <v>10</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -798,69 +866,81 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Barié et al., 2020</t>
+          <t>Butt et al., 2024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Barié et al., 2020</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BPTB</t>
+          <t>HT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>QT</t>
+          <t>PLT</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="I6" t="n">
-        <v>1.05</v>
+        <v>89.7</v>
       </c>
       <c r="J6" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="N6" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>29</v>
+      </c>
+      <c r="R6" t="n">
+        <v>29</v>
+      </c>
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>17</v>
-      </c>
-      <c r="P6" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>13</v>
-      </c>
-      <c r="R6" t="n">
-        <v>13</v>
-      </c>
-      <c r="S6" t="n">
-        <v>123.6</v>
-      </c>
       <c r="T6" t="n">
-        <v>123.6</v>
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>60</v>
+      </c>
+      <c r="V6" t="n">
+        <v>60</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -868,16 +948,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bi et al., 2018</t>
+          <t>Calvert et al., 2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bi et al., 2018</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -887,38 +967,38 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PLT</t>
+          <t>QT</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="H7" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="I7" t="n">
-        <v>1.71</v>
+        <v>92</v>
       </c>
       <c r="J7" t="n">
-        <v>1.85</v>
+        <v>89</v>
       </c>
       <c r="K7" t="n">
-        <v>0.57</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.77</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="N7" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="O7" t="n">
-        <v>34</v>
+        <v>7.7</v>
       </c>
       <c r="P7" t="n">
-        <v>34</v>
+        <v>7.7</v>
       </c>
       <c r="Q7" t="n">
         <v>28</v>
@@ -927,10 +1007,22 @@
         <v>28</v>
       </c>
       <c r="S7" t="n">
-        <v>29.7</v>
+        <v>27</v>
       </c>
       <c r="T7" t="n">
-        <v>29.7</v>
+        <v>27</v>
+      </c>
+      <c r="U7" t="n">
+        <v>24</v>
+      </c>
+      <c r="V7" t="n">
+        <v>24</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -938,69 +1030,81 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
+        <v>32</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Guglielmetti et al., 2021</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ikdc_subjective</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BPTB</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>31</v>
+      </c>
+      <c r="H8" t="n">
+        <v>31</v>
+      </c>
+      <c r="I8" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>91</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="M8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="Q8" t="n">
         <v>23</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ejerhed et al., 2003</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Ejerhed et al., 2003</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>BPTB</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>32</v>
-      </c>
-      <c r="H8" t="n">
-        <v>34</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="M8" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="N8" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="O8" t="n">
-        <v>25</v>
-      </c>
-      <c r="P8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>9</v>
-      </c>
       <c r="R8" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8</v>
+      </c>
+      <c r="U8" t="n">
         <v>24</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>24</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1008,61 +1112,81 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eriksson et al., 2001</t>
+          <t>Horstmann et al., 2022</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Eriksson et al., 2001</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BPTB</t>
+          <t>HT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HT</t>
+          <t>QT</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="H9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="I9" t="n">
-        <v>0.95</v>
+        <v>83.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>89.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.91</v>
+        <v>12.7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.95</v>
+        <v>12.2</v>
       </c>
       <c r="M9" t="n">
-        <v>27</v>
+        <v>32.7</v>
       </c>
       <c r="N9" t="n">
-        <v>27</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+        <v>32.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+      <c r="R9" t="n">
+        <v>12</v>
+      </c>
       <c r="S9" t="n">
-        <v>6.7</v>
+        <v>15</v>
       </c>
       <c r="T9" t="n">
-        <v>6.7</v>
+        <v>15</v>
+      </c>
+      <c r="U9" t="n">
+        <v>24</v>
+      </c>
+      <c r="V9" t="n">
+        <v>24</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1070,16 +1194,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Feller &amp; Webster, 2003</t>
+          <t>Iliopoulos et al., 2017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Feller &amp; Webster, 2003</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1093,34 +1217,34 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H10" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>83.2</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>82.78</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>26.3</v>
+        <v>24.8</v>
       </c>
       <c r="N10" t="n">
-        <v>26.3</v>
+        <v>24.8</v>
       </c>
       <c r="O10" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
         <v>10</v>
@@ -1129,10 +1253,22 @@
         <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V10" t="n">
+        <v>9</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
@@ -1140,16 +1276,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gifstad et al., 2013</t>
+          <t>Komzak et al., 2022</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gifstad et al., 2013</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1159,42 +1295,62 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HT</t>
+          <t>QT</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H11" t="n">
         <v>36</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>74.2</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4</v>
+        <v>78.3</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8</v>
+        <v>10.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="M11" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="N11" t="n">
-        <v>27</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="O11" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>23</v>
+      </c>
+      <c r="R11" t="n">
+        <v>23</v>
+      </c>
       <c r="S11" t="n">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="T11" t="n">
-        <v>84</v>
+        <v>17</v>
+      </c>
+      <c r="U11" t="n">
+        <v>28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>28</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -1202,57 +1358,81 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Harilainen et al., 2006</t>
+          <t>Li et al., 2015</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Harilainen et al., 2006</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BPTB</t>
+          <t>HT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HT</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H12" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>87.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2</v>
+        <v>83.8</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="M12" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>17</v>
+      </c>
+      <c r="R12" t="n">
+        <v>17</v>
+      </c>
       <c r="S12" t="n">
-        <v>60.6</v>
+        <v>15</v>
       </c>
       <c r="T12" t="n">
-        <v>60.6</v>
+        <v>15</v>
+      </c>
+      <c r="U12" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="V12" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5.8</v>
       </c>
     </row>
     <row r="13">
@@ -1260,69 +1440,81 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Holm et al., 2010</t>
+          <t>Lind et al., 2020</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Holm et al., 2010</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BPTB</t>
+          <t>HT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HT</t>
+          <t>QT</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H13" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="J13" t="n">
+        <v>82</v>
+      </c>
+      <c r="K13" t="n">
+        <v>18</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14</v>
+      </c>
+      <c r="M13" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>25</v>
+      </c>
+      <c r="R13" t="n">
+        <v>25</v>
+      </c>
+      <c r="S13" t="n">
+        <v>24</v>
+      </c>
+      <c r="T13" t="n">
+        <v>24</v>
+      </c>
+      <c r="U13" t="n">
+        <v>24</v>
+      </c>
+      <c r="V13" t="n">
+        <v>24</v>
+      </c>
+      <c r="W13" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="N13" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="O13" t="n">
-        <v>15</v>
-      </c>
-      <c r="P13" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>14</v>
-      </c>
-      <c r="R13" t="n">
-        <v>14</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>10.7</v>
+      <c r="X13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1330,69 +1522,73 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Horstmann et al., 2022</t>
+          <t>Lucidi et al., 2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Horstmann et al., 2022</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>BPTB</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>HT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>QT</t>
-        </is>
-      </c>
       <c r="G14" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>13.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="M14" t="n">
-        <v>24.1</v>
+        <v>52.8</v>
       </c>
       <c r="N14" t="n">
-        <v>24.1</v>
+        <v>52.8</v>
       </c>
       <c r="O14" t="n">
-        <v>21</v>
+        <v>7.3</v>
       </c>
       <c r="P14" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>24</v>
-      </c>
-      <c r="T14" t="n">
-        <v>24</v>
+        <v>7.3</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="n">
+        <v>240</v>
+      </c>
+      <c r="V14" t="n">
+        <v>240</v>
+      </c>
+      <c r="W14" t="n">
+        <v>20</v>
+      </c>
+      <c r="X14" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1400,16 +1596,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jansson et al., 2003</t>
+          <t>Lui et al., 2012</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jansson et al., 2003</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1423,34 +1619,58 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>2.63</v>
+        <v>15.2</v>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+        <v>12.3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>14</v>
+      </c>
+      <c r="R15" t="n">
+        <v>14</v>
+      </c>
       <c r="S15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>24</v>
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>12</v>
+      </c>
+      <c r="V15" t="n">
+        <v>12</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1458,16 +1678,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kautzner et al., 2015</t>
+          <t>Lund et al., 2014</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kautzner et al., 2015</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1477,50 +1697,62 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HT</t>
+          <t>QT</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="H16" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>75</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>76</v>
       </c>
       <c r="K16" t="n">
-        <v>0.21</v>
+        <v>13</v>
       </c>
       <c r="L16" t="n">
-        <v>0.42</v>
+        <v>16</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="n">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="R16" t="n">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
         <v>24</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>24</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1528,69 +1760,81 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Konrads et al., 2016</t>
+          <t>Malik et al., 2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Konrads et al., 2016</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BPTB</t>
+          <t>HT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HT</t>
+          <t>PLT</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.51</v>
+        <v>7.4</v>
       </c>
       <c r="L17" t="n">
-        <v>0.78</v>
+        <v>6.3</v>
       </c>
       <c r="M17" t="n">
-        <v>29.8</v>
+        <v>28.12</v>
       </c>
       <c r="N17" t="n">
-        <v>29.8</v>
+        <v>28.12</v>
       </c>
       <c r="O17" t="n">
-        <v>23</v>
+        <v>5.21</v>
       </c>
       <c r="P17" t="n">
-        <v>23</v>
+        <v>5.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="R17" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="S17" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>120</v>
+        <v>7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -1598,16 +1842,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Laoruengthana et al., 2009</t>
+          <t>Matsumoto et al., 2006</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Laoruengthana et al., 2009</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1621,38 +1865,58 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H18" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="I18" t="n">
-        <v>1.22</v>
+        <v>84.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.96</v>
+        <v>86.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6899999999999999</v>
+        <v>11</v>
       </c>
       <c r="L18" t="n">
-        <v>0.42</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>28.7</v>
+        <v>23.7</v>
       </c>
       <c r="N18" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+        <v>23.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>21</v>
+      </c>
+      <c r="R18" t="n">
+        <v>21</v>
+      </c>
       <c r="S18" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="T18" t="n">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="U18" t="n">
+        <v>87</v>
+      </c>
+      <c r="V18" t="n">
+        <v>87</v>
+      </c>
+      <c r="W18" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>7.3</v>
       </c>
     </row>
     <row r="19">
@@ -1660,16 +1924,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Laxdal et al., 2005</t>
+          <t>Moraiti et al., 2010</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Laxdal et al., 2005</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1683,38 +1947,58 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5</v>
+        <v>90</v>
       </c>
       <c r="K19" t="n">
-        <v>3.01</v>
+        <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>3.12</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N19" t="n">
-        <v>25</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6</v>
+      </c>
       <c r="S19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>21</v>
+      </c>
+      <c r="V19" t="n">
+        <v>21</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="20">
@@ -1722,69 +2006,77 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Li et al., 2015</t>
+          <t>Papalia et al., 2015</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Li et al., 2015</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>BPTB</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>HT</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>TA</t>
-        </is>
-      </c>
       <c r="G20" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>90.97</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6</v>
+        <v>11.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="M20" t="n">
-        <v>30.5</v>
+        <v>24.7</v>
       </c>
       <c r="N20" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>15</v>
-      </c>
-      <c r="P20" t="n">
-        <v>15</v>
-      </c>
+        <v>24.7</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>73.2</v>
+        <v>20</v>
       </c>
       <c r="T20" t="n">
-        <v>73.2</v>
+        <v>20</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -1792,69 +2084,81 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lidén et al., 2007</t>
+          <t>Sinding et al., 2020</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lidén et al., 2007</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BPTB</t>
+          <t>HT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HT</t>
+          <t>QT</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="H21" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>76</v>
       </c>
       <c r="J21" t="n">
-        <v>2.7</v>
+        <v>76</v>
       </c>
       <c r="K21" t="n">
-        <v>3.06</v>
+        <v>15</v>
       </c>
       <c r="L21" t="n">
-        <v>3.39</v>
+        <v>17</v>
       </c>
       <c r="M21" t="n">
-        <v>29</v>
+        <v>28.3</v>
       </c>
       <c r="N21" t="n">
-        <v>29</v>
+        <v>28.3</v>
       </c>
       <c r="O21" t="n">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="P21" t="n">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="S21" t="n">
-        <v>87.09999999999999</v>
+        <v>20</v>
       </c>
       <c r="T21" t="n">
-        <v>87.09999999999999</v>
+        <v>20</v>
+      </c>
+      <c r="U21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1862,69 +2166,81 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lind et al., 2020</t>
+          <t>Smith et al., 2020</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lind et al., 2020</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>BPTB</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>HT</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>QT</t>
-        </is>
-      </c>
       <c r="G22" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="H22" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8</v>
+        <v>94.8</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="M22" t="n">
-        <v>27.2</v>
+        <v>17.7</v>
       </c>
       <c r="N22" t="n">
-        <v>27.2</v>
+        <v>17.7</v>
       </c>
       <c r="O22" t="n">
-        <v>29</v>
+        <v>2.4</v>
       </c>
       <c r="P22" t="n">
-        <v>29</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="R22" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="S22" t="n">
+        <v>17</v>
+      </c>
+      <c r="T22" t="n">
+        <v>17</v>
+      </c>
+      <c r="U22" t="n">
         <v>24</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>24</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1932,16 +2248,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lucidi et al., 2025</t>
+          <t>Sonnery-cottet et al., 2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Lucidi et al., 2025</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1955,38 +2271,58 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>19</v>
+        <v>296</v>
       </c>
       <c r="H23" t="n">
-        <v>20</v>
+        <v>297</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5</v>
+        <v>91</v>
       </c>
       <c r="K23" t="n">
-        <v>1.6</v>
+        <v>10.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2</v>
+        <v>10.3</v>
       </c>
       <c r="M23" t="n">
-        <v>54.5</v>
+        <v>24.8</v>
       </c>
       <c r="N23" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+        <v>24.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>214</v>
+      </c>
+      <c r="R23" t="n">
+        <v>214</v>
+      </c>
       <c r="S23" t="n">
-        <v>240</v>
+        <v>69</v>
       </c>
       <c r="T23" t="n">
-        <v>240</v>
+        <v>69</v>
+      </c>
+      <c r="U23" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>5.1</v>
       </c>
     </row>
     <row r="24">
@@ -1994,69 +2330,81 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lui et al., 2012</t>
+          <t>Tang et al., 2023</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lui et al., 2012</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BPTB</t>
+          <t>HT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HT</t>
+          <t>QT</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H24" t="n">
         <v>17</v>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>90.13</v>
       </c>
       <c r="J24" t="n">
-        <v>3.1</v>
+        <v>87.12</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4</v>
+        <v>6.99</v>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>6.61</v>
       </c>
       <c r="M24" t="n">
-        <v>24.6</v>
+        <v>28.31</v>
       </c>
       <c r="N24" t="n">
-        <v>24.6</v>
+        <v>28.31</v>
       </c>
       <c r="O24" t="n">
-        <v>38</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>38</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>24</v>
+      </c>
+      <c r="V24" t="n">
+        <v>24</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2064,21 +2412,21 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lund et al., 2014</t>
+          <t>Vilchez-Cavazos et al., 2020</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lund et al., 2014</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BPTB</t>
+          <t>HT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2087,46 +2435,58 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>90</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8</v>
+        <v>88.17</v>
       </c>
       <c r="K25" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>2.49</v>
       </c>
       <c r="M25" t="n">
-        <v>30</v>
+        <v>24.46</v>
       </c>
       <c r="N25" t="n">
-        <v>30</v>
+        <v>24.46</v>
       </c>
       <c r="O25" t="n">
-        <v>17</v>
+        <v>8.24</v>
       </c>
       <c r="P25" t="n">
-        <v>17</v>
+        <v>8.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R25" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S25" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>12</v>
+      </c>
+      <c r="V25" t="n">
+        <v>12</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2134,69 +2494,81 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malik et al., 2026</t>
+          <t>Wipfler et al., 2011</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Malik et al., 2026</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>BPTB</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>HT</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>PLT</t>
-        </is>
-      </c>
       <c r="G26" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H26" t="n">
         <v>25</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>86.72</v>
       </c>
       <c r="J26" t="n">
-        <v>1.8</v>
+        <v>92.95</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2.27</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9</v>
+        <v>1.99</v>
       </c>
       <c r="M26" t="n">
-        <v>27.8</v>
+        <v>29.87</v>
       </c>
       <c r="N26" t="n">
-        <v>27.8</v>
+        <v>29.87</v>
       </c>
       <c r="O26" t="n">
-        <v>17</v>
+        <v>7.3</v>
       </c>
       <c r="P26" t="n">
-        <v>17</v>
+        <v>7.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="R26" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T26" t="n">
-        <v>6</v>
+        <v>12</v>
+      </c>
+      <c r="U26" t="n">
+        <v>108</v>
+      </c>
+      <c r="V26" t="n">
+        <v>108</v>
+      </c>
+      <c r="W26" t="n">
+        <v>9</v>
+      </c>
+      <c r="X26" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -2204,16 +2576,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Matsumoto et al., 2006</t>
+          <t>Zaffagnini et al., 2011</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Matsumoto et al., 2006</t>
+          <t>ikdc_subjective</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2227,598 +2599,58 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H27" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>82</v>
       </c>
       <c r="J27" t="n">
-        <v>1.7</v>
+        <v>88</v>
       </c>
       <c r="K27" t="n">
-        <v>2.1</v>
+        <v>20</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>9</v>
       </c>
       <c r="M27" t="n">
-        <v>24.4</v>
+        <v>26</v>
       </c>
       <c r="N27" t="n">
-        <v>24.4</v>
+        <v>26</v>
       </c>
       <c r="O27" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q27" t="n">
         <v>20</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>20</v>
       </c>
-      <c r="Q27" t="n">
-        <v>15</v>
-      </c>
-      <c r="R27" t="n">
-        <v>15</v>
-      </c>
       <c r="S27" t="n">
-        <v>80.7</v>
+        <v>19</v>
       </c>
       <c r="T27" t="n">
-        <v>80.7</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="n">
-        <v>76</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Pinczewski et al., 2007</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Pinczewski et al., 2007</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>BPTB</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>54</v>
-      </c>
-      <c r="H28" t="n">
-        <v>58</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M28" t="n">
-        <v>24</v>
-      </c>
-      <c r="N28" t="n">
-        <v>24</v>
-      </c>
-      <c r="O28" t="n">
-        <v>47</v>
-      </c>
-      <c r="P28" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>43</v>
-      </c>
-      <c r="R28" t="n">
-        <v>43</v>
-      </c>
-      <c r="S28" t="n">
-        <v>120</v>
-      </c>
-      <c r="T28" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="n">
-        <v>77</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Popovic et al., 2024</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Popovic et al., 2024</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>BPTB</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>38</v>
-      </c>
-      <c r="H29" t="n">
-        <v>33</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>27</v>
-      </c>
-      <c r="N29" t="n">
-        <v>27</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="n">
-        <v>228</v>
-      </c>
-      <c r="T29" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="n">
-        <v>85</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Smith et al., 2020</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Smith et al., 2020</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>BPTB</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>32</v>
-      </c>
-      <c r="H30" t="n">
-        <v>32</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M30" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="N30" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="O30" t="n">
-        <v>13</v>
-      </c>
-      <c r="P30" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q30" t="n">
         <v>19</v>
       </c>
-      <c r="R30" t="n">
-        <v>19</v>
-      </c>
-      <c r="S30" t="n">
-        <v>24</v>
-      </c>
-      <c r="T30" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="n">
-        <v>87</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Sonnery-cottet et al., 2026</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Sonnery-cottet et al., 2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>BPTB</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>296</v>
-      </c>
-      <c r="H31" t="n">
-        <v>297</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="O31" t="n">
-        <v>233</v>
-      </c>
-      <c r="P31" t="n">
-        <v>233</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>40</v>
-      </c>
-      <c r="R31" t="n">
-        <v>40</v>
-      </c>
-      <c r="S31" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="T31" t="n">
-        <v>63.9</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="n">
-        <v>95</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Webster et al., 2001</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Webster et al., 2001</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>BPTB</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>23</v>
-      </c>
-      <c r="H32" t="n">
-        <v>31</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="M32" t="n">
-        <v>27</v>
-      </c>
-      <c r="N32" t="n">
-        <v>27</v>
-      </c>
-      <c r="O32" t="n">
-        <v>23</v>
-      </c>
-      <c r="P32" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>10</v>
-      </c>
-      <c r="R32" t="n">
-        <v>10</v>
-      </c>
-      <c r="S32" t="n">
-        <v>24</v>
-      </c>
-      <c r="T32" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="n">
-        <v>96</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Wipfler et al., 2011</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Wipfler et al., 2011</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>BPTB</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>29</v>
-      </c>
-      <c r="H33" t="n">
-        <v>25</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M33" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="O33" t="n">
-        <v>18</v>
-      </c>
-      <c r="P33" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>13</v>
-      </c>
-      <c r="R33" t="n">
-        <v>13</v>
-      </c>
-      <c r="S33" t="n">
-        <v>108</v>
-      </c>
-      <c r="T33" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="n">
-        <v>97</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yadav et al., 2025</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Yadav et al., 2025</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>QT</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>36</v>
-      </c>
-      <c r="H34" t="n">
-        <v>33</v>
-      </c>
-      <c r="I34" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M34" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="N34" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="O34" t="n">
-        <v>30</v>
-      </c>
-      <c r="P34" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>12</v>
-      </c>
-      <c r="T34" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="n">
-        <v>100</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Zaffagnini et al., 2011</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Zaffagnini et al., 2011</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>BPTB</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>40</v>
-      </c>
-      <c r="H35" t="n">
-        <v>39</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M35" t="n">
-        <v>27</v>
-      </c>
-      <c r="N35" t="n">
-        <v>27</v>
-      </c>
-      <c r="O35" t="n">
-        <v>22</v>
-      </c>
-      <c r="P35" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>18</v>
-      </c>
-      <c r="R35" t="n">
-        <v>18</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="U27" t="n">
         <v>103.2</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V27" t="n">
         <v>103.2</v>
+      </c>
+      <c r="W27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
